--- a/dell_monitors_transformed.xlsx
+++ b/dell_monitors_transformed.xlsx
@@ -2941,7 +2941,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>DELL Monitor - P2722HE</v>
+        <v>Dell 27 USB-C Hub Monitor - P2722HE</v>
       </c>
       <c r="B80" t="str">
         <v>P2722HE</v>
@@ -2953,22 +2953,22 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E80" t="str">
-        <v>"27 Inch"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F80" t="str">
-        <v/>
+        <v>1920 x 1080 FHD</v>
       </c>
       <c r="G80" t="str">
         <v>5ms</v>
       </c>
       <c r="H80" t="str">
-        <v/>
+        <v>60Hz</v>
       </c>
       <c r="I80" t="str">
-        <v>HDMI, DisplayPort, USB-C, RJ-45</v>
+        <v>1 HDMI, 1 DisplayPort, 1 DisplayPort Out (MST), 1 USB-C (65W Power Delivery), 4 USB Type-A, 1 RJ-45 Ethernet, Audio Out</v>
       </c>
       <c r="J80" t="str">
-        <v/>
+        <v>3 Years</v>
       </c>
     </row>
   </sheetData>

--- a/dell_monitors_transformed.xlsx
+++ b/dell_monitors_transformed.xlsx
@@ -1481,10 +1481,10 @@
         <v>DELL E Series LED Monitor</v>
       </c>
       <c r="E34" t="str">
-        <v>22"</v>
+        <v>21.5 Inch</v>
       </c>
       <c r="F34" t="str">
-        <v/>
+        <v>1920 x 1080 FHD</v>
       </c>
       <c r="G34" t="str">
         <v>5.0ms</v>

--- a/dell_monitors_transformed.xlsx
+++ b/dell_monitors_transformed.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J79"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
@@ -457,7 +457,7 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E2" t="str">
-        <v>14"</v>
+        <v>14 Inch</v>
       </c>
       <c r="F2" t="str">
         <v>1920 x 1200 WUXGA</v>
@@ -489,7 +489,7 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E3" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F3" t="str">
         <v>1920 x 1200 WUXGA</v>
@@ -521,7 +521,7 @@
         <v>DELL SE Series LED Monitor</v>
       </c>
       <c r="E4" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F4" t="str">
         <v>2560 x 1440 QHD</v>
@@ -553,10 +553,10 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E5" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>1920 x 1200</v>
       </c>
       <c r="G5" t="str">
         <v>5.0ms</v>
@@ -585,10 +585,10 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E6" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>1920 x 1200</v>
       </c>
       <c r="G6" t="str">
         <v>5.0ms</v>
@@ -617,10 +617,10 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E7" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>1920 x 1200</v>
       </c>
       <c r="G7" t="str">
         <v>5.0ms</v>
@@ -649,10 +649,10 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E8" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>1920 x 1200</v>
       </c>
       <c r="G8" t="str">
         <v>5.0ms</v>
@@ -681,10 +681,10 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E9" t="str">
-        <v>34"</v>
+        <v>34 Inch</v>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>3440 x 1440 UWQHD</v>
       </c>
       <c r="G9" t="str">
         <v>5.0ms</v>
@@ -713,10 +713,10 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E10" t="str">
-        <v>34"</v>
+        <v>34 Inch</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>3440 x 1440 UWQHD</v>
       </c>
       <c r="G10" t="str">
         <v>5.0ms</v>
@@ -745,7 +745,7 @@
         <v>Dell UltraSharp Series LED Monitor</v>
       </c>
       <c r="E11" t="str">
-        <v>32"</v>
+        <v>32 Inch</v>
       </c>
       <c r="F11" t="str">
         <v>3840 x 2160 4K UHD</v>
@@ -777,7 +777,7 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E12" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F12" t="str">
         <v>1920 x 1200 WUXGA</v>
@@ -809,7 +809,7 @@
         <v>DELL S Series LED Monitor</v>
       </c>
       <c r="E13" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F13" t="str">
         <v>3840 x 2160 4K UHD</v>
@@ -841,7 +841,7 @@
         <v>Dell Alienware Series LED Monitor</v>
       </c>
       <c r="E14" t="str">
-        <v>32"</v>
+        <v>32 Inch</v>
       </c>
       <c r="F14" t="str">
         <v>2560 x 1440 QHD</v>
@@ -873,7 +873,7 @@
         <v>Dell UltraSharp Series LED Monitor</v>
       </c>
       <c r="E15" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F15" t="str">
         <v>3840 x 2160 4K UHD</v>
@@ -905,7 +905,7 @@
         <v>Dell Alienware Series LED Monitor</v>
       </c>
       <c r="E16" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F16" t="str">
         <v>2560 x 1440 QHD</v>
@@ -937,7 +937,7 @@
         <v>DELL S Series LED Monitor</v>
       </c>
       <c r="E17" t="str">
-        <v>32"</v>
+        <v>32 Inch</v>
       </c>
       <c r="F17" t="str">
         <v>3840 x 2160 4K UHD</v>
@@ -1001,7 +1001,7 @@
         <v>DELL S Series LED Monitor</v>
       </c>
       <c r="E19" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F19" t="str">
         <v>3840 x 2160 4K UHD</v>
@@ -1033,7 +1033,7 @@
         <v>Dell Alienware Series LED Monitor</v>
       </c>
       <c r="E20" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F20" t="str">
         <v>2560 x 1440 QHD</v>
@@ -1065,7 +1065,7 @@
         <v>DELL S Series LED Monitor</v>
       </c>
       <c r="E21" t="str">
-        <v>34"</v>
+        <v>34 Inch</v>
       </c>
       <c r="F21" t="str">
         <v>3440 x 1440 UWQHD</v>
@@ -1097,7 +1097,7 @@
         <v>DELL S Series LED Monitor</v>
       </c>
       <c r="E22" t="str">
-        <v>32"</v>
+        <v>32 Inch</v>
       </c>
       <c r="F22" t="str">
         <v>3840 x 2160 4K UHD</v>
@@ -1129,10 +1129,10 @@
         <v>DELL E Series LED Monitor</v>
       </c>
       <c r="E23" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>1920 x 1080 FHD</v>
       </c>
       <c r="G23" t="str">
         <v>5.0ms</v>
@@ -1161,7 +1161,7 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E24" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F24" t="str">
         <v>2560 x 1440 QHD</v>
@@ -1193,7 +1193,7 @@
         <v>Dell Alienware Series LED Monitor</v>
       </c>
       <c r="E25" t="str">
-        <v>34"</v>
+        <v>34 Inch</v>
       </c>
       <c r="F25" t="str">
         <v>2560 x 1440 QHD</v>
@@ -1225,7 +1225,7 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E26" t="str">
-        <v>32"</v>
+        <v>32 Inch</v>
       </c>
       <c r="F26" t="str">
         <v>3840 x 2160 4K UHD</v>
@@ -1257,10 +1257,10 @@
         <v>DELL E Series LED Monitor</v>
       </c>
       <c r="E27" t="str">
-        <v>24"</v>
+        <v>23.8 Inch</v>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>1920 x 1080 FHD</v>
       </c>
       <c r="G27" t="str">
         <v>8.0ms</v>
@@ -1289,7 +1289,7 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E28" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F28" t="str">
         <v>2560 x 1440 QHD</v>
@@ -1321,7 +1321,7 @@
         <v>DELL SE Series LED Monitor</v>
       </c>
       <c r="E29" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F29" t="str">
         <v>1920 x 1080 FHD</v>
@@ -1353,7 +1353,7 @@
         <v>Dell UltraSharp Series LED Monitor</v>
       </c>
       <c r="E30" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F30" t="str">
         <v>2560 x 1440 QHD</v>
@@ -1385,7 +1385,7 @@
         <v>Dell UltraSharp Series LED Monitor</v>
       </c>
       <c r="E31" t="str">
-        <v>32"</v>
+        <v>32 Inch</v>
       </c>
       <c r="F31" t="str">
         <v>3840 x 2160 4K UHD</v>
@@ -1417,7 +1417,7 @@
         <v>Dell Alienware Series LED Monitor</v>
       </c>
       <c r="E32" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F32" t="str">
         <v>2560 x 1440 QHD</v>
@@ -1449,7 +1449,7 @@
         <v>Dell Alienware Series LED Monitor</v>
       </c>
       <c r="E33" t="str">
-        <v>25"</v>
+        <v>25 Inch</v>
       </c>
       <c r="F33" t="str">
         <v>1920 x 1080 FHD</v>
@@ -1513,10 +1513,10 @@
         <v>DELL S Series LED Monitor</v>
       </c>
       <c r="E35" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F35" t="str">
-        <v/>
+        <v>1920 x 1080 FHD</v>
       </c>
       <c r="G35" t="str">
         <v>1.0ms</v>
@@ -1545,7 +1545,7 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E36" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F36" t="str">
         <v>2560 x 1440 QHD</v>
@@ -1577,10 +1577,10 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E37" t="str">
-        <v>34"</v>
+        <v>34 Inch</v>
       </c>
       <c r="F37" t="str">
-        <v/>
+        <v>3440 x 1440 UWQHD</v>
       </c>
       <c r="G37" t="str">
         <v>5.0ms</v>
@@ -1609,7 +1609,7 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E38" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F38" t="str">
         <v>3840 x 2160 4K UHD</v>
@@ -1641,10 +1641,10 @@
         <v>DELL E Series LED Monitor</v>
       </c>
       <c r="E39" t="str">
-        <v>22"</v>
+        <v>22 Inch</v>
       </c>
       <c r="F39" t="str">
-        <v/>
+        <v>1920 x 1080 FHD</v>
       </c>
       <c r="G39" t="str">
         <v>5.0ms</v>
@@ -1673,10 +1673,10 @@
         <v>DELL E Series LED Monitor</v>
       </c>
       <c r="E40" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F40" t="str">
-        <v/>
+        <v>1920 x 1080 FHD</v>
       </c>
       <c r="G40" t="str">
         <v>8.0ms</v>
@@ -1705,7 +1705,7 @@
         <v>Dell Alienware Series LED Monitor</v>
       </c>
       <c r="E41" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F41" t="str">
         <v>2560 x 1440 QHD</v>
@@ -1737,7 +1737,7 @@
         <v>Dell UltraSharp Series LED Monitor</v>
       </c>
       <c r="E42" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F42" t="str">
         <v>2560 x 1440 QHD</v>
@@ -1769,10 +1769,10 @@
         <v>Dell UltraSharp Series LED Monitor</v>
       </c>
       <c r="E43" t="str">
-        <v>34"</v>
+        <v>34 Inch</v>
       </c>
       <c r="F43" t="str">
-        <v/>
+        <v>3440 x 1440 UWQHD</v>
       </c>
       <c r="G43" t="str">
         <v>8.0ms</v>
@@ -1801,7 +1801,7 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E44" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F44" t="str">
         <v>2560 x 1440 QHD</v>
@@ -1833,7 +1833,7 @@
         <v>DELL S Series LED Monitor</v>
       </c>
       <c r="E45" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F45" t="str">
         <v>2560 x 1440 QHD</v>
@@ -1865,7 +1865,7 @@
         <v>Dell UltraSharp Series LED Monitor</v>
       </c>
       <c r="E46" t="str">
-        <v>38"</v>
+        <v>38 Inch</v>
       </c>
       <c r="F46" t="str">
         <v>3840 x 1600</v>
@@ -1897,10 +1897,10 @@
         <v>DELL S Series LED Monitor</v>
       </c>
       <c r="E47" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F47" t="str">
-        <v/>
+        <v>1920 x 1080 FHD</v>
       </c>
       <c r="G47" t="str">
         <v>1.0ms</v>
@@ -1929,7 +1929,7 @@
         <v>DELL SE Series LED Monitor</v>
       </c>
       <c r="E48" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F48" t="str">
         <v>1920 x 1080 FHD</v>
@@ -1961,10 +1961,10 @@
         <v>DELL E Series LED Monitor</v>
       </c>
       <c r="E49" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F49" t="str">
-        <v/>
+        <v>1920 x 1080 FHD</v>
       </c>
       <c r="G49" t="str">
         <v>5.0ms</v>
@@ -1993,7 +1993,7 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E50" t="str">
-        <v>34"</v>
+        <v>34 Inch</v>
       </c>
       <c r="F50" t="str">
         <v>3440 x 1440 UWQHD</v>
@@ -2025,7 +2025,7 @@
         <v>DELL E Series LED Monitor</v>
       </c>
       <c r="E51" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F51" t="str">
         <v>2560 x 1440 QHD</v>
@@ -2057,7 +2057,7 @@
         <v>DELL S Series LED Monitor</v>
       </c>
       <c r="E52" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F52" t="str">
         <v>2560 x 1440 QHD</v>
@@ -2089,10 +2089,10 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E53" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F53" t="str">
-        <v/>
+        <v>1920 x 1200</v>
       </c>
       <c r="G53" t="str">
         <v>5.0ms</v>
@@ -2121,7 +2121,7 @@
         <v>DELL SE Series LED Monitor</v>
       </c>
       <c r="E54" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F54" t="str">
         <v>1920 x 1080 FHD</v>
@@ -2153,7 +2153,7 @@
         <v>DELL SE Series LED Monitor</v>
       </c>
       <c r="E55" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F55" t="str">
         <v>1920 x 1080 FHD</v>
@@ -2185,7 +2185,7 @@
         <v>DELL SE Series LED Monitor</v>
       </c>
       <c r="E56" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F56" t="str">
         <v>1920 x 1080 FHD</v>
@@ -2217,10 +2217,10 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E57" t="str">
-        <v>22"</v>
+        <v>22 Inch</v>
       </c>
       <c r="F57" t="str">
-        <v/>
+        <v>1920 x 1200</v>
       </c>
       <c r="G57" t="str">
         <v>5.0ms</v>
@@ -2249,10 +2249,10 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E58" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F58" t="str">
-        <v/>
+        <v>1920 x 1200</v>
       </c>
       <c r="G58" t="str">
         <v>5.0ms</v>
@@ -2281,10 +2281,10 @@
         <v>DELL E Series LED Monitor</v>
       </c>
       <c r="E59" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F59" t="str">
-        <v/>
+        <v>1920 x 1080 FHD</v>
       </c>
       <c r="G59" t="str">
         <v>5.0ms</v>
@@ -2313,10 +2313,10 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E60" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F60" t="str">
-        <v/>
+        <v>1920 x 1200</v>
       </c>
       <c r="G60" t="str">
         <v>5.0ms</v>
@@ -2345,10 +2345,10 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E61" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F61" t="str">
-        <v/>
+        <v>1920 x 1200</v>
       </c>
       <c r="G61" t="str">
         <v>5.0ms</v>
@@ -2377,7 +2377,7 @@
         <v>Dell UltraSharp Series LED Monitor</v>
       </c>
       <c r="E62" t="str">
-        <v>43"</v>
+        <v>43 Inch</v>
       </c>
       <c r="F62" t="str">
         <v>3840 x 2160 4K UHD</v>
@@ -2409,7 +2409,7 @@
         <v>Dell Alienware Series LED Monitor</v>
       </c>
       <c r="E63" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F63" t="str">
         <v>2560 x 1440 QHD</v>
@@ -2441,10 +2441,10 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E64" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F64" t="str">
-        <v/>
+        <v>1920 x 1200</v>
       </c>
       <c r="G64" t="str">
         <v>5.0ms</v>
@@ -2473,7 +2473,7 @@
         <v>Dell UltraSharp Series LED Monitor</v>
       </c>
       <c r="E65" t="str">
-        <v>49"</v>
+        <v>49 Inch</v>
       </c>
       <c r="F65" t="str">
         <v>5120 x 1440</v>
@@ -2505,10 +2505,10 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E66" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F66" t="str">
-        <v/>
+        <v>1920 x 1200</v>
       </c>
       <c r="G66" t="str">
         <v>5.0ms</v>
@@ -2537,7 +2537,7 @@
         <v>Dell Alienware Series LED Monitor</v>
       </c>
       <c r="E67" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F67" t="str">
         <v>2560 x 1440 QHD</v>
@@ -2569,10 +2569,10 @@
         <v>Dell UltraSharp Series LED Monitor</v>
       </c>
       <c r="E68" t="str">
-        <v>52"</v>
+        <v>52 Inch</v>
       </c>
       <c r="F68" t="str">
-        <v/>
+        <v>5120 x 1440</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2601,7 +2601,7 @@
         <v>DELL SE Series LED Monitor</v>
       </c>
       <c r="E69" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F69" t="str">
         <v>1920 x 1080 FHD</v>
@@ -2633,7 +2633,7 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E70" t="str">
-        <v>27"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F70" t="str">
         <v>1920 x 1080 FHD</v>
@@ -2665,7 +2665,7 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E71" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F71" t="str">
         <v>1920 x 1200 WUXGA</v>
@@ -2697,7 +2697,7 @@
         <v>Dell Alienware Series LED Monitor</v>
       </c>
       <c r="E72" t="str">
-        <v>34"</v>
+        <v>34 Inch</v>
       </c>
       <c r="F72" t="str">
         <v>2560 x 1440 QHD</v>
@@ -2729,7 +2729,7 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E73" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F73" t="str">
         <v>1920 x 1200 WUXGA</v>
@@ -2761,7 +2761,7 @@
         <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E74" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F74" t="str">
         <v>1920 x 1200 WUXGA</v>
@@ -2793,7 +2793,7 @@
         <v>Dell UltraSharp Series LED Monitor</v>
       </c>
       <c r="E75" t="str">
-        <v>32"</v>
+        <v>32 Inch</v>
       </c>
       <c r="F75" t="str">
         <v>3840 x 2160 4K UHD</v>
@@ -2825,7 +2825,7 @@
         <v>Dell UltraSharp Series LED Monitor</v>
       </c>
       <c r="E76" t="str">
-        <v>24"</v>
+        <v>24 Inch</v>
       </c>
       <c r="F76" t="str">
         <v>1920 x 1080 FHD</v>
@@ -2845,42 +2845,42 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>DELL Monitor - TEST12345</v>
+        <v>DELL Monitor - SE2425HM</v>
       </c>
       <c r="B77" t="str">
-        <v>TEST12345</v>
+        <v>SE2425HM</v>
       </c>
       <c r="C77" t="str">
         <v>DELL</v>
       </c>
       <c r="D77" t="str">
-        <v>Dell Monitor</v>
+        <v>DELL SE Series LED Monitor</v>
       </c>
       <c r="E77" t="str">
-        <v>""</v>
+        <v>23.8 Inch</v>
       </c>
       <c r="F77" t="str">
-        <v/>
+        <v>1920 x 1080 FHD</v>
       </c>
       <c r="G77" t="str">
-        <v/>
+        <v>5ms</v>
       </c>
       <c r="H77" t="str">
-        <v/>
+        <v>100 Hz</v>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>1 HDMI (HDCP 1.4), 1 VGA</v>
       </c>
       <c r="J77" t="str">
-        <v/>
+        <v>3 Years</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>DELL Monitor - SE2425HM</v>
+        <v>DELL Monitor - SE2425HG</v>
       </c>
       <c r="B78" t="str">
-        <v>SE2425HM</v>
+        <v>SE2425HG</v>
       </c>
       <c r="C78" t="str">
         <v>DELL</v>
@@ -2889,91 +2889,59 @@
         <v>DELL SE Series LED Monitor</v>
       </c>
       <c r="E78" t="str">
-        <v>"23.8 Inch"</v>
+        <v>23.8 Inch</v>
       </c>
       <c r="F78" t="str">
         <v>1920 x 1080 FHD</v>
       </c>
       <c r="G78" t="str">
-        <v>5ms</v>
+        <v>1ms</v>
       </c>
       <c r="H78" t="str">
-        <v>100 Hz</v>
+        <v>200Hz</v>
       </c>
       <c r="I78" t="str">
-        <v>1 HDMI (HDCP 1.4), 1 VGA</v>
+        <v>2 HDMI ports, 1 DisplayPort 1.4, 1 Headphone-out port (3.5 mm jack)</v>
       </c>
       <c r="J78" t="str">
-        <v>3 Years</v>
+        <v>3 Year</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>DELL Monitor - SE2425HG</v>
+        <v>Dell 27 USB-C Hub Monitor - P2722HE</v>
       </c>
       <c r="B79" t="str">
-        <v>SE2425HG</v>
+        <v>P2722HE</v>
       </c>
       <c r="C79" t="str">
         <v>DELL</v>
       </c>
       <c r="D79" t="str">
-        <v>DELL SE Series LED Monitor</v>
+        <v>DELL Pro Series LED Monitor</v>
       </c>
       <c r="E79" t="str">
-        <v>"23.8 Inch"</v>
+        <v>27 Inch</v>
       </c>
       <c r="F79" t="str">
         <v>1920 x 1080 FHD</v>
       </c>
       <c r="G79" t="str">
-        <v>1ms</v>
+        <v>5ms</v>
       </c>
       <c r="H79" t="str">
-        <v>200Hz</v>
+        <v>60Hz</v>
       </c>
       <c r="I79" t="str">
-        <v>2 HDMI ports, 1 DisplayPort 1.4, 1 Headphone-out port (3.5 mm jack)</v>
+        <v>1 HDMI, 1 DisplayPort, 1 DisplayPort Out (MST), 1 USB-C (65W Power Delivery), 4 USB Type-A, 1 RJ-45 Ethernet, Audio Out</v>
       </c>
       <c r="J79" t="str">
-        <v>3 Year</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>Dell 27 USB-C Hub Monitor - P2722HE</v>
-      </c>
-      <c r="B80" t="str">
-        <v>P2722HE</v>
-      </c>
-      <c r="C80" t="str">
-        <v>DELL</v>
-      </c>
-      <c r="D80" t="str">
-        <v>DELL Pro Series LED Monitor</v>
-      </c>
-      <c r="E80" t="str">
-        <v>27 Inch</v>
-      </c>
-      <c r="F80" t="str">
-        <v>1920 x 1080 FHD</v>
-      </c>
-      <c r="G80" t="str">
-        <v>5ms</v>
-      </c>
-      <c r="H80" t="str">
-        <v>60Hz</v>
-      </c>
-      <c r="I80" t="str">
-        <v>1 HDMI, 1 DisplayPort, 1 DisplayPort Out (MST), 1 USB-C (65W Power Delivery), 4 USB Type-A, 1 RJ-45 Ethernet, Audio Out</v>
-      </c>
-      <c r="J80" t="str">
         <v>3 Years</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J80"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J79"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dell_monitors_transformed.xlsx
+++ b/dell_monitors_transformed.xlsx
@@ -466,7 +466,7 @@
         <v>7.0ms</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>60Hz</v>
       </c>
       <c r="I2" t="str">
         <v>2 USB-C, 1 DisplayPort</v>
@@ -498,7 +498,7 @@
         <v>5.0ms</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>60Hz</v>
       </c>
       <c r="I3" t="str">
         <v>1 HDMI, 1 DisplayPort, 2 USB-C, Ethernet</v>
@@ -594,7 +594,7 @@
         <v>5.0ms</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>120Hz</v>
       </c>
       <c r="I6" t="str">
         <v>1 HDMI, 2 DisplayPort (1 in, 1 out), USB-C</v>
@@ -658,7 +658,7 @@
         <v>5.0ms</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>100Hz</v>
       </c>
       <c r="I8" t="str">
         <v>1 HDMI, 2 DisplayPort (1 in, 1 out), USB-C</v>
@@ -751,7 +751,7 @@
         <v>3840 x 2160 4K UHD</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>0.1ms</v>
       </c>
       <c r="H11" t="str">
         <v>120Hz</v>
@@ -847,7 +847,7 @@
         <v>2560 x 1440 QHD</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>0.1ms</v>
       </c>
       <c r="H14" t="str">
         <v>240Hz</v>
@@ -879,7 +879,7 @@
         <v>3840 x 2160 4K UHD</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>8.0ms</v>
       </c>
       <c r="H15" t="str">
         <v>120Hz</v>
@@ -911,7 +911,7 @@
         <v>2560 x 1440 QHD</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>0.1ms</v>
       </c>
       <c r="H16" t="str">
         <v>280Hz</v>
@@ -1039,7 +1039,7 @@
         <v>2560 x 1440 QHD</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>0.1ms</v>
       </c>
       <c r="H20" t="str">
         <v>360Hz</v>
@@ -1103,7 +1103,7 @@
         <v>3840 x 2160 4K UHD</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>5.0ms</v>
       </c>
       <c r="H22" t="str">
         <v>120Hz</v>
@@ -1199,7 +1199,7 @@
         <v>2560 x 1440 QHD</v>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>1.0ms</v>
       </c>
       <c r="H25" t="str">
         <v>240Hz</v>
@@ -1391,7 +1391,7 @@
         <v>3840 x 2160 4K UHD</v>
       </c>
       <c r="G31" t="str">
-        <v/>
+        <v>8.0ms</v>
       </c>
       <c r="H31" t="str">
         <v>120Hz</v>
@@ -1423,7 +1423,7 @@
         <v>2560 x 1440 QHD</v>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>0.1ms</v>
       </c>
       <c r="H32" t="str">
         <v>240Hz</v>
@@ -1586,7 +1586,7 @@
         <v>5.0ms</v>
       </c>
       <c r="H37" t="str">
-        <v/>
+        <v>100Hz</v>
       </c>
       <c r="I37" t="str">
         <v>1 HDMI, 1 DisplayPort, 1 USB-C</v>
@@ -1874,7 +1874,7 @@
         <v>5.0ms</v>
       </c>
       <c r="H46" t="str">
-        <v/>
+        <v>60Hz</v>
       </c>
       <c r="I46" t="str">
         <v>DisplayPort, HDMI, USB-C, Thunderbolt, Ethernet</v>
@@ -2002,7 +2002,7 @@
         <v>5.0ms</v>
       </c>
       <c r="H50" t="str">
-        <v/>
+        <v>60Hz</v>
       </c>
       <c r="I50" t="str">
         <v>1 HDMI, 1 USB-C</v>
@@ -2386,7 +2386,7 @@
         <v>5.0ms</v>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>60Hz</v>
       </c>
       <c r="I62" t="str">
         <v>DisplayPort, HDMI, USB-C, Thunderbolt, Ethernet</v>
@@ -2479,10 +2479,10 @@
         <v>5120 x 1440</v>
       </c>
       <c r="G65" t="str">
-        <v/>
+        <v>8.0ms</v>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>60Hz</v>
       </c>
       <c r="I65" t="str">
         <v>DisplayPort, HDMI, USB-C, Thunderbolt</v>
@@ -2543,7 +2543,7 @@
         <v>2560 x 1440 QHD</v>
       </c>
       <c r="G67" t="str">
-        <v/>
+        <v>1.0ms</v>
       </c>
       <c r="H67" t="str">
         <v>240Hz</v>
@@ -2575,7 +2575,7 @@
         <v>5120 x 1440</v>
       </c>
       <c r="G68" t="str">
-        <v/>
+        <v>5.0ms</v>
       </c>
       <c r="H68" t="str">
         <v>120Hz</v>
@@ -2799,10 +2799,10 @@
         <v>3840 x 2160 4K UHD</v>
       </c>
       <c r="G75" t="str">
-        <v/>
+        <v>6.0ms</v>
       </c>
       <c r="H75" t="str">
-        <v/>
+        <v>60Hz</v>
       </c>
       <c r="I75" t="str">
         <v>DisplayPort, HDMI, USB-C, Thunderbolt, Ethernet</v>
